--- a/Coca Cola - DCF Valuation/CocaCola - DCF (Updated).xlsx
+++ b/Coca Cola - DCF Valuation/CocaCola - DCF (Updated).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Môj PC\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9AB58334-6F43-464A-B0B0-B6541C30C6EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BDF13C7-C8B0-4568-90C0-0F57973137C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="85">
   <si>
     <t>Discounted Cash Flow Valuation</t>
   </si>
@@ -56,9 +56,6 @@
     <t>Simon Norrman</t>
   </si>
   <si>
-    <t>22 Febraury 2026</t>
-  </si>
-  <si>
     <t>This model estimates the intrinsic value of The Coca-Cola Company using a 5-year DCF approach based on publicly available financial data</t>
   </si>
   <si>
@@ -185,15 +182,6 @@
     <t>NOPAT</t>
   </si>
   <si>
-    <t>Free Cash Flow</t>
-  </si>
-  <si>
-    <t>*Historical revenue growth averaged 5,5% from 2021-2025; therefore the assumption of 4% makes sense</t>
-  </si>
-  <si>
-    <t>*I will treat CapEx as a postive reinvestment amount in this model, and then subtract it later in the FCF</t>
-  </si>
-  <si>
     <t>Forecast Financials (2026-2030)</t>
   </si>
   <si>
@@ -290,21 +278,6 @@
     <t>*Data from the Coca Cola 10K</t>
   </si>
   <si>
-    <t>Formula to find total debt = Current maturities of long term debt + Long-term debt</t>
-  </si>
-  <si>
-    <t>Total Debt = 1,822 + 42,119 = 43,941</t>
-  </si>
-  <si>
-    <t>Then to find Net Debt = Total Debt - Cash (Total Cash, Cahs Equivalents and Short-Term Investments)</t>
-  </si>
-  <si>
-    <t>Net Debt = 43,941-13,872=30,069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sensitivity </t>
-  </si>
-  <si>
     <t>Implied Share Price Sensitivity (WACC vs Terminal Growth)</t>
   </si>
   <si>
@@ -315,22 +288,30 @@
   </si>
   <si>
     <t>Terminal Growth</t>
+  </si>
+  <si>
+    <t>22 February 2026</t>
+  </si>
+  <si>
+    <t>Unlevered Free Cash Flow</t>
+  </si>
+  <si>
+    <t>Sensitivity Analysis</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="7">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
-    <numFmt numFmtId="166" formatCode="#.##00_);\(##,#00\)"/>
     <numFmt numFmtId="167" formatCode="0.000"/>
     <numFmt numFmtId="168" formatCode="#.0_);\(#.0\)"/>
     <numFmt numFmtId="169" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* \-??_ ;_-@_ "/>
     <numFmt numFmtId="170" formatCode="_(\$* #,##0.00_);_(\$* \(#,##0.00\);_(\$* \-??_);_(@_)"/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -341,36 +322,6 @@
     <font>
       <b/>
       <sz val="20"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="238"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="238"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="238"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="238"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -504,8 +455,49 @@
       <family val="2"/>
       <charset val="238"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -544,12 +536,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFE2C5"/>
-        <bgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="31">
+  <borders count="36">
     <border>
       <left/>
       <right/>
@@ -868,30 +872,79 @@
         <color theme="1"/>
       </left>
       <right/>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right/>
       <top/>
       <bottom style="thin">
-        <color theme="1"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right style="thin">
-        <color theme="1"/>
+        <color indexed="64"/>
       </right>
       <top/>
       <bottom style="thin">
-        <color theme="1"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="170" fontId="22" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="22" fillId="0" borderId="0"/>
+    <xf numFmtId="170" fontId="18" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="18" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -899,36 +952,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
@@ -951,78 +992,139 @@
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="16" fillId="5" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="22" fillId="0" borderId="0" xfId="2" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="16" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="18" fillId="0" borderId="0" xfId="2" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="12" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="7"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="16" fillId="6" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="20" fillId="6" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="16" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="16" fillId="7" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="16" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="18" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="18" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="16" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="22" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" textRotation="90"/>
     </xf>
-    <xf numFmtId="10" fontId="16" fillId="7" borderId="27" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="18" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="16" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="18" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="18" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="18" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="12" fillId="5" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="19" fillId="7" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="19" fillId="7" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="19" fillId="8" borderId="27" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="19" fillId="7" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="19" fillId="7" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="19" fillId="8" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="19" fillId="7" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="20" fillId="7" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="18" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="20" fillId="7" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="20" fillId="7" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="20" fillId="8" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="20" fillId="7" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="20" fillId="7" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="20" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="20" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="20" fillId="7" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="20" fillId="8" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="20" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="20" fillId="8" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="20" fillId="7" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="20" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="20" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="20" fillId="7" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -1108,6 +1210,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1284,6 +1390,28 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="5">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{A5E23612-4589-409B-B79D-57462FAC479F}">
+  <we:reference id="WA200009404" version="1.0.0.8" store="Omex" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200009404" version="1.0.0.8" store="WA200009404" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;4be28ab8-1755-4b13-8920-890c0c39ef2f&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A10:S34"/>
@@ -1300,8 +1428,8 @@
       <c r="R10" s="2"/>
       <c r="S10" s="2"/>
     </row>
-    <row r="11" spans="13:19" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="M11" s="3" t="s">
+    <row r="11" spans="13:19" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="M11" s="82" t="s">
         <v>1</v>
       </c>
       <c r="N11" s="2"/>
@@ -1312,7 +1440,7 @@
       <c r="S11" s="2"/>
     </row>
     <row r="12" spans="13:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="M12" s="4" t="s">
+      <c r="M12" s="79" t="s">
         <v>2</v>
       </c>
       <c r="N12" s="2"/>
@@ -1323,7 +1451,7 @@
       <c r="S12" s="2"/>
     </row>
     <row r="13" spans="13:19" x14ac:dyDescent="0.25">
-      <c r="M13" s="5"/>
+      <c r="M13" s="3"/>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" s="2"/>
@@ -1341,7 +1469,7 @@
       <c r="S14" s="2"/>
     </row>
     <row r="15" spans="13:19" x14ac:dyDescent="0.25">
-      <c r="M15" s="6" t="s">
+      <c r="M15" s="80" t="s">
         <v>3</v>
       </c>
       <c r="N15" s="2"/>
@@ -1352,8 +1480,8 @@
       <c r="S15" s="2"/>
     </row>
     <row r="16" spans="13:19" x14ac:dyDescent="0.25">
-      <c r="M16" s="6" t="s">
-        <v>4</v>
+      <c r="M16" s="80" t="s">
+        <v>82</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -1363,7 +1491,7 @@
       <c r="S16" s="2"/>
     </row>
     <row r="17" spans="13:19" x14ac:dyDescent="0.25">
-      <c r="M17" s="5"/>
+      <c r="M17" s="3"/>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" s="2"/>
@@ -1381,8 +1509,8 @@
       <c r="S18" s="2"/>
     </row>
     <row r="19" spans="13:19" x14ac:dyDescent="0.25">
-      <c r="M19" s="7" t="s">
-        <v>5</v>
+      <c r="M19" s="81" t="s">
+        <v>4</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -1392,8 +1520,8 @@
       <c r="S19" s="2"/>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" s="8" t="s">
-        <v>6</v>
+      <c r="A34" s="4" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1412,206 +1540,206 @@
     <col min="3" max="3" width="8.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:11" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="10" t="s">
-        <v>7</v>
+    <row r="2" spans="1:11" s="5" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="6" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" s="7" t="s">
         <v>9</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="12">
+        <v>10</v>
+      </c>
+      <c r="C5" s="8">
         <v>46076</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="14"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="15"/>
-      <c r="I7" s="16"/>
-      <c r="J7" s="16"/>
-      <c r="K7" s="16"/>
+        <v>7</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="10"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="12"/>
+      <c r="K7" s="12"/>
     </row>
     <row r="8" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="9" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="14"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="16"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B10" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="18"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="20"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B10" s="21" t="s">
+      <c r="C10" s="18"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="20">
+        <v>5.5E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B11" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="22"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="24">
+      <c r="C11" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="22"/>
+      <c r="E11" s="23">
+        <v>0.29499999999999998</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B12" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" s="22"/>
+      <c r="E12" s="23">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B13" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" s="22"/>
+      <c r="E13" s="23">
+        <v>2.5000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B14" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="22"/>
+      <c r="E14" s="23">
         <v>0.04</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B11" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D11" s="26"/>
-      <c r="E11" s="27">
-        <v>0.28000000000000003</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B12" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="D12" s="26"/>
-      <c r="E12" s="27">
-        <v>0.23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B13" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="D13" s="26"/>
-      <c r="E13" s="27">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B14" s="25" t="s">
+    <row r="15" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="26"/>
-      <c r="E14" s="27">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15" s="29"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="31">
+      <c r="C15" s="25"/>
+      <c r="D15" s="26"/>
+      <c r="E15" s="27">
         <v>0.01</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="17" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>8</v>
-      </c>
-      <c r="B17" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="14"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="16"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B18" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="C17" s="18"/>
-      <c r="D17" s="19"/>
-      <c r="E17" s="20"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B18" s="21" t="s">
+      <c r="C18" s="18"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="28">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B19" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="22"/>
-      <c r="D18" s="23"/>
-      <c r="E18" s="32">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B19" s="25" t="s">
+      <c r="D19" s="22"/>
+      <c r="E19" s="29">
+        <v>5.5E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B20" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="D19" s="26"/>
-      <c r="E19" s="33">
-        <v>5.5E-2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B20" s="25" t="s">
+      <c r="D20" s="22"/>
+      <c r="E20" s="30">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B21" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="D20" s="26"/>
-      <c r="E20" s="34">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B21" s="25" t="s">
+      <c r="D21" s="22"/>
+      <c r="E21" s="29">
+        <v>4.4999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B22" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="D21" s="26"/>
-      <c r="E21" s="33">
-        <v>4.4999999999999998E-2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B22" s="25" t="s">
+      <c r="D22" s="22"/>
+      <c r="E22" s="31">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="D22" s="26"/>
-      <c r="E22" s="35">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="28" t="s">
-        <v>27</v>
-      </c>
-      <c r="C23" s="29"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="36">
+      <c r="C23" s="25"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="32">
         <v>0.7</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="25" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>8</v>
-      </c>
-      <c r="B25" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25" s="14"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="16"/>
+    </row>
+    <row r="26" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="C25" s="18"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="20"/>
-    </row>
-    <row r="26" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="28" t="s">
-        <v>29</v>
-      </c>
-      <c r="C26" s="29"/>
-      <c r="D26" s="30"/>
-      <c r="E26" s="37">
-        <v>2.5000000000000001E-2</v>
+      <c r="C26" s="25"/>
+      <c r="D26" s="26"/>
+      <c r="E26" s="84">
+        <v>2.75E-2</v>
       </c>
     </row>
   </sheetData>
@@ -1634,392 +1762,388 @@
     <col min="12" max="17" width="16.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:7" s="38" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="39" t="s">
+    <row r="2" spans="1:7" s="33" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="34" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B4" s="35" t="s">
         <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="40" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5" s="42">
+        <v>7</v>
+      </c>
+      <c r="B5" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="37">
         <v>2021</v>
       </c>
-      <c r="D5" s="42">
+      <c r="D5" s="37">
         <f>C5+1</f>
         <v>2022</v>
       </c>
-      <c r="E5" s="42">
+      <c r="E5" s="37">
         <f>D5+1</f>
         <v>2023</v>
       </c>
-      <c r="F5" s="42">
+      <c r="F5" s="37">
         <f>E5+1</f>
         <v>2024</v>
       </c>
-      <c r="G5" s="42">
+      <c r="G5" s="37">
         <f>F5+1</f>
         <v>2025</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="38">
+        <v>38655</v>
+      </c>
+      <c r="D6" s="38">
+        <v>43004</v>
+      </c>
+      <c r="E6" s="38">
+        <v>45754</v>
+      </c>
+      <c r="F6" s="38">
+        <v>47061</v>
+      </c>
+      <c r="G6" s="38">
+        <v>47941</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="43">
-        <v>38655</v>
-      </c>
-      <c r="D6" s="43">
-        <v>43004</v>
-      </c>
-      <c r="E6" s="43">
-        <v>45754</v>
-      </c>
-      <c r="F6" s="43">
-        <v>47061</v>
-      </c>
-      <c r="G6" s="43">
-        <v>47941</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="44" t="s">
+      <c r="C7" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="45" t="s">
-        <v>35</v>
-      </c>
-      <c r="D7" s="46">
+      <c r="D7" s="41">
         <f>(D6/C6)-1</f>
         <v>0.11250808433579107</v>
       </c>
-      <c r="E7" s="46">
+      <c r="E7" s="41">
         <f>(E6/D6)-1</f>
         <v>6.3947539763743011E-2</v>
       </c>
-      <c r="F7" s="46">
+      <c r="F7" s="41">
         <f>(F6/E6)-1</f>
         <v>2.8565808453905772E-2</v>
       </c>
-      <c r="G7" s="46">
+      <c r="G7" s="41">
         <f>(G6/F6)-1</f>
         <v>1.8699135164998548E-2</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C8" s="43">
+        <v>35</v>
+      </c>
+      <c r="C8" s="38">
         <v>10308</v>
       </c>
-      <c r="D8" s="43">
+      <c r="D8" s="38">
         <v>10909</v>
       </c>
-      <c r="E8" s="43">
+      <c r="E8" s="38">
         <v>11311</v>
       </c>
-      <c r="F8" s="43">
+      <c r="F8" s="38">
         <v>9992</v>
       </c>
-      <c r="G8" s="43">
+      <c r="G8" s="38">
         <v>13762</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="44" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="46">
+      <c r="B9" s="39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="41">
         <f>C8/C6</f>
         <v>0.26666666666666666</v>
       </c>
-      <c r="D9" s="46">
+      <c r="D9" s="41">
         <f>D8/D6</f>
         <v>0.25367407683006232</v>
       </c>
-      <c r="E9" s="46">
+      <c r="E9" s="41">
         <f>E8/E6</f>
         <v>0.24721335839489444</v>
       </c>
-      <c r="F9" s="46">
+      <c r="F9" s="41">
         <f>F8/F6</f>
         <v>0.21232018019166612</v>
       </c>
-      <c r="G9" s="46">
+      <c r="G9" s="41">
         <f>G8/G6</f>
         <v>0.28706117936630443</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" s="43">
+        <v>36</v>
+      </c>
+      <c r="C10" s="38">
         <v>12425</v>
       </c>
-      <c r="D10" s="43">
+      <c r="D10" s="38">
         <v>11686</v>
       </c>
-      <c r="E10" s="43">
+      <c r="E10" s="38">
         <v>12925</v>
       </c>
-      <c r="F10" s="43">
+      <c r="F10" s="38">
         <v>13086</v>
       </c>
-      <c r="G10" s="43">
+      <c r="G10" s="38">
         <v>15998</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="38">
+        <v>2621</v>
+      </c>
+      <c r="D11" s="38">
+        <v>2115</v>
+      </c>
+      <c r="E11" s="38">
+        <v>2249</v>
+      </c>
+      <c r="F11" s="38">
+        <v>2437</v>
+      </c>
+      <c r="G11" s="38">
+        <v>2861</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="C11" s="43">
-        <v>2621</v>
-      </c>
-      <c r="D11" s="43">
-        <v>2115</v>
-      </c>
-      <c r="E11" s="43">
-        <v>2249</v>
-      </c>
-      <c r="F11" s="43">
-        <v>2437</v>
-      </c>
-      <c r="G11" s="43">
-        <v>2861</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="44" t="s">
-        <v>39</v>
-      </c>
-      <c r="C12" s="46">
+      <c r="C12" s="41">
         <f>C11/C10</f>
         <v>0.21094567404426559</v>
       </c>
-      <c r="D12" s="46">
+      <c r="D12" s="41">
         <f>D11/D10</f>
         <v>0.18098579496833819</v>
       </c>
-      <c r="E12" s="46">
+      <c r="E12" s="41">
         <f>E11/E10</f>
         <v>0.17400386847195357</v>
       </c>
-      <c r="F12" s="46">
+      <c r="F12" s="41">
         <f>F11/F10</f>
         <v>0.18622955830658719</v>
       </c>
-      <c r="G12" s="46">
+      <c r="G12" s="41">
         <f>G11/G10</f>
         <v>0.17883485435679461</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>40</v>
-      </c>
-      <c r="C13" s="43">
+        <v>39</v>
+      </c>
+      <c r="C13" s="38">
         <v>9771</v>
       </c>
-      <c r="D13" s="43">
+      <c r="D13" s="38">
         <v>9542</v>
       </c>
-      <c r="E13" s="43">
+      <c r="E13" s="38">
         <v>10714</v>
       </c>
-      <c r="F13" s="43">
+      <c r="F13" s="38">
         <v>10631</v>
       </c>
-      <c r="G13" s="43">
+      <c r="G13" s="38">
         <v>13107</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>8</v>
-      </c>
-      <c r="B16" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="C16" s="13">
+        <v>7</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" s="9">
         <v>2021</v>
       </c>
-      <c r="D16" s="13">
+      <c r="D16" s="9">
         <f>C16+1</f>
         <v>2022</v>
       </c>
-      <c r="E16" s="13">
+      <c r="E16" s="9">
         <f>D16+1</f>
         <v>2023</v>
       </c>
-      <c r="F16" s="13">
+      <c r="F16" s="9">
         <f>E16+1</f>
         <v>2024</v>
       </c>
-      <c r="G16" s="13">
+      <c r="G16" s="9">
         <f>F16+1</f>
         <v>2025</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>42</v>
-      </c>
-      <c r="C17" s="43">
+        <v>41</v>
+      </c>
+      <c r="C17" s="38">
         <v>1425</v>
       </c>
-      <c r="D17" s="43">
+      <c r="D17" s="38">
         <v>1260</v>
       </c>
-      <c r="E17" s="43">
+      <c r="E17" s="38">
         <v>1128</v>
       </c>
-      <c r="F17" s="43">
+      <c r="F17" s="38">
         <v>1075</v>
       </c>
-      <c r="G17" s="43">
+      <c r="G17" s="38">
         <v>1050</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>43</v>
-      </c>
-      <c r="C18" s="43">
+        <v>42</v>
+      </c>
+      <c r="C18" s="38">
         <v>1367</v>
       </c>
-      <c r="D18" s="43">
+      <c r="D18" s="38">
         <v>1484</v>
       </c>
-      <c r="E18" s="43">
+      <c r="E18" s="38">
         <v>1852</v>
       </c>
-      <c r="F18" s="43">
+      <c r="F18" s="38">
         <v>2064</v>
       </c>
-      <c r="G18" s="43">
+      <c r="G18" s="38">
         <v>2112</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>44</v>
-      </c>
-      <c r="C19" s="43">
-        <v>1325</v>
-      </c>
-      <c r="D19" s="47">
-        <v>-605</v>
-      </c>
-      <c r="E19" s="47">
-        <v>-846</v>
-      </c>
-      <c r="F19" s="47">
-        <v>-6234</v>
-      </c>
-      <c r="G19" s="47">
-        <v>-7208</v>
+        <v>43</v>
+      </c>
+      <c r="C19" s="38">
+        <v>-1325</v>
+      </c>
+      <c r="D19" s="38">
+        <v>605</v>
+      </c>
+      <c r="E19" s="38">
+        <v>846</v>
+      </c>
+      <c r="F19" s="38">
+        <v>6234</v>
+      </c>
+      <c r="G19" s="38">
+        <v>7208</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>8</v>
-      </c>
-      <c r="B22" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="C22" s="48">
+        <v>7</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C22" s="42">
         <v>2021</v>
       </c>
-      <c r="D22" s="48">
+      <c r="D22" s="42">
         <f>C22+1</f>
         <v>2022</v>
       </c>
-      <c r="E22" s="48">
+      <c r="E22" s="42">
         <f>D22+1</f>
         <v>2023</v>
       </c>
-      <c r="F22" s="48">
+      <c r="F22" s="42">
         <f>E22+1</f>
         <v>2024</v>
       </c>
-      <c r="G22" s="48">
+      <c r="G22" s="42">
         <f>F22+1</f>
         <v>2025</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>46</v>
-      </c>
-      <c r="C23" s="43">
+        <v>45</v>
+      </c>
+      <c r="C23" s="38">
         <v>8134</v>
       </c>
-      <c r="D23" s="43">
+      <c r="D23" s="38">
         <v>8935</v>
       </c>
-      <c r="E23" s="43">
+      <c r="E23" s="38">
         <v>9343</v>
       </c>
-      <c r="F23" s="43">
+      <c r="F23" s="38">
         <v>8131</v>
       </c>
-      <c r="G23" s="43">
+      <c r="G23" s="38">
         <v>11301</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>47</v>
-      </c>
-      <c r="C24" s="43">
+        <v>83</v>
+      </c>
+      <c r="C24" s="38">
         <f>C23+C17-C18-C19</f>
-        <v>6867</v>
-      </c>
-      <c r="D24" s="43">
+        <v>9517</v>
+      </c>
+      <c r="D24" s="38">
         <f>D23+D17-D18-D19</f>
-        <v>9316</v>
-      </c>
-      <c r="E24" s="43">
+        <v>8106</v>
+      </c>
+      <c r="E24" s="38">
         <f>E23+E17-E18-E19</f>
-        <v>9465</v>
-      </c>
-      <c r="F24" s="43">
+        <v>7773</v>
+      </c>
+      <c r="F24" s="38">
         <f>F23+F17-F18-F19</f>
-        <v>13376</v>
-      </c>
-      <c r="G24" s="43">
+        <v>908</v>
+      </c>
+      <c r="G24" s="38">
         <f>G23+G17-G18-G19</f>
-        <v>17447</v>
+        <v>3031</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D29" s="49"/>
-      <c r="F29" s="50"/>
+      <c r="D29" s="43"/>
+      <c r="F29" s="44"/>
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B33" s="8" t="s">
-        <v>48</v>
-      </c>
+      <c r="B33" s="4"/>
     </row>
     <row r="34" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B34" s="8" t="s">
-        <v>49</v>
-      </c>
+      <c r="B34" s="4"/>
     </row>
     <row r="35" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B35" s="51"/>
+      <c r="B35" s="45"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2037,350 +2161,350 @@
     <col min="3" max="7" width="16.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:7" s="52" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:7" s="52" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="53" t="s">
-        <v>50</v>
+    <row r="2" spans="1:7" s="46" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:7" s="46" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="47" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="40" t="s">
-        <v>31</v>
+      <c r="B5" s="35" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="54" t="s">
-        <v>51</v>
-      </c>
-      <c r="C6" s="13">
+        <v>7</v>
+      </c>
+      <c r="B6" s="48" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" s="9">
         <v>2026</v>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="9">
         <f>C6+1</f>
         <v>2027</v>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="9">
         <f>D6+1</f>
         <v>2028</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="9">
         <f>E6+1</f>
         <v>2029</v>
       </c>
-      <c r="G6" s="13">
+      <c r="G6" s="9">
         <f>F6+1</f>
         <v>2030</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="38">
+        <f>'Historical Financials'!G6*(1+Assumptions!$E$10)</f>
+        <v>50577.754999999997</v>
+      </c>
+      <c r="D7" s="38">
+        <f>C7*(1+Assumptions!$E$10)</f>
+        <v>53359.531524999991</v>
+      </c>
+      <c r="E7" s="38">
+        <f>D7*(1+Assumptions!$E$10)</f>
+        <v>56294.305758874987</v>
+      </c>
+      <c r="F7" s="38">
+        <f>E7*(1+Assumptions!$E$10)</f>
+        <v>59390.492575613105</v>
+      </c>
+      <c r="G7" s="38">
+        <f>F7*(1+Assumptions!$E$10)</f>
+        <v>62656.96966727182</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="C7" s="43">
-        <f>'Historical Financials'!G6*(1+Assumptions!$E$10)</f>
-        <v>49858.64</v>
-      </c>
-      <c r="D7" s="43">
-        <f>C7*(1+Assumptions!$E$10)</f>
-        <v>51852.9856</v>
-      </c>
-      <c r="E7" s="43">
-        <f>D7*(1+Assumptions!$E$10)</f>
-        <v>53927.105024000004</v>
-      </c>
-      <c r="F7" s="43">
-        <f>E7*(1+Assumptions!$E$10)</f>
-        <v>56084.189224960006</v>
-      </c>
-      <c r="G7" s="43">
-        <f>F7*(1+Assumptions!$E$10)</f>
-        <v>58327.556793958407</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="44" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" s="55">
+      <c r="C8" s="49">
         <f>Assumptions!$E$10</f>
-        <v>0.04</v>
-      </c>
-      <c r="D8" s="55">
+        <v>5.5E-2</v>
+      </c>
+      <c r="D8" s="49">
         <f>Assumptions!$E$10</f>
-        <v>0.04</v>
-      </c>
-      <c r="E8" s="55">
+        <v>5.5E-2</v>
+      </c>
+      <c r="E8" s="49">
         <f>Assumptions!$E$10</f>
-        <v>0.04</v>
-      </c>
-      <c r="F8" s="55">
+        <v>5.5E-2</v>
+      </c>
+      <c r="F8" s="49">
         <f>Assumptions!$E$10</f>
-        <v>0.04</v>
-      </c>
-      <c r="G8" s="55">
+        <v>5.5E-2</v>
+      </c>
+      <c r="G8" s="49">
         <f>Assumptions!$E$10</f>
-        <v>0.04</v>
+        <v>5.5E-2</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="44" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="55">
+      <c r="B9" s="39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="49">
         <f>Assumptions!$E$11</f>
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="D9" s="55">
+        <v>0.29499999999999998</v>
+      </c>
+      <c r="D9" s="49">
         <f>Assumptions!$E$11</f>
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="E9" s="55">
+        <v>0.29499999999999998</v>
+      </c>
+      <c r="E9" s="49">
         <f>Assumptions!$E$11</f>
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="F9" s="55">
+        <v>0.29499999999999998</v>
+      </c>
+      <c r="F9" s="49">
         <f>Assumptions!$E$11</f>
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="G9" s="55">
+        <v>0.29499999999999998</v>
+      </c>
+      <c r="G9" s="49">
         <f>Assumptions!$E$11</f>
-        <v>0.28000000000000003</v>
+        <v>0.29499999999999998</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>52</v>
-      </c>
-      <c r="C10" s="43">
+        <v>48</v>
+      </c>
+      <c r="C10" s="38">
         <f>C7*C9</f>
-        <v>13960.4192</v>
-      </c>
-      <c r="D10" s="43">
+        <v>14920.437724999998</v>
+      </c>
+      <c r="D10" s="38">
         <f>D7*D9</f>
-        <v>14518.835968000001</v>
-      </c>
-      <c r="E10" s="43">
+        <v>15741.061799874997</v>
+      </c>
+      <c r="E10" s="38">
         <f>E7*E9</f>
-        <v>15099.589406720002</v>
-      </c>
-      <c r="F10" s="43">
+        <v>16606.820198868121</v>
+      </c>
+      <c r="F10" s="38">
         <f>F7*F9</f>
-        <v>15703.572982988802</v>
-      </c>
-      <c r="G10" s="43">
+        <v>17520.195309805866</v>
+      </c>
+      <c r="G10" s="38">
         <f>G7*G9</f>
-        <v>16331.715902308355</v>
+        <v>18483.806051845186</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="55">
+        <v>16</v>
+      </c>
+      <c r="C11" s="49">
         <f>Assumptions!$E$12</f>
         <v>0.23</v>
       </c>
-      <c r="D11" s="55">
+      <c r="D11" s="49">
         <f>Assumptions!$E$12</f>
         <v>0.23</v>
       </c>
-      <c r="E11" s="55">
+      <c r="E11" s="49">
         <f>Assumptions!$E$12</f>
         <v>0.23</v>
       </c>
-      <c r="F11" s="55">
+      <c r="F11" s="49">
         <f>Assumptions!$E$12</f>
         <v>0.23</v>
       </c>
-      <c r="G11" s="55">
+      <c r="G11" s="49">
         <f>Assumptions!$E$12</f>
         <v>0.23</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>46</v>
-      </c>
-      <c r="C12" s="43">
+        <v>45</v>
+      </c>
+      <c r="C12" s="38">
         <f>C10*(1-C11)</f>
-        <v>10749.522784000001</v>
-      </c>
-      <c r="D12" s="43">
+        <v>11488.737048249999</v>
+      </c>
+      <c r="D12" s="38">
         <f>D10*(1-D11)</f>
-        <v>11179.503695360001</v>
-      </c>
-      <c r="E12" s="43">
+        <v>12120.617585903748</v>
+      </c>
+      <c r="E12" s="38">
         <f>E10*(1-E11)</f>
-        <v>11626.683843174402</v>
-      </c>
-      <c r="F12" s="43">
+        <v>12787.251553128453</v>
+      </c>
+      <c r="F12" s="38">
         <f>F10*(1-F11)</f>
-        <v>12091.751196901378</v>
-      </c>
-      <c r="G12" s="43">
+        <v>13490.550388550517</v>
+      </c>
+      <c r="G12" s="38">
         <f>G10*(1-G11)</f>
-        <v>12575.421244777433</v>
+        <v>14232.530659920792</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>8</v>
-      </c>
-      <c r="B15" s="54" t="s">
-        <v>53</v>
-      </c>
-      <c r="C15" s="13">
+        <v>7</v>
+      </c>
+      <c r="B15" s="48" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" s="9">
         <v>2026</v>
       </c>
-      <c r="D15" s="13">
+      <c r="D15" s="9">
         <f>C15+1</f>
         <v>2027</v>
       </c>
-      <c r="E15" s="13">
+      <c r="E15" s="9">
         <f>D15+1</f>
         <v>2028</v>
       </c>
-      <c r="F15" s="13">
+      <c r="F15" s="9">
         <f>E15+1</f>
         <v>2029</v>
       </c>
-      <c r="G15" s="13">
+      <c r="G15" s="9">
         <f>F15+1</f>
         <v>2030</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>54</v>
-      </c>
-      <c r="C16" s="43">
+        <v>50</v>
+      </c>
+      <c r="C16" s="38">
         <f>C7*Assumptions!$E$13</f>
-        <v>2492.9320000000002</v>
-      </c>
-      <c r="D16" s="43">
+        <v>1264.4438749999999</v>
+      </c>
+      <c r="D16" s="38">
         <f>D7*Assumptions!$E$13</f>
-        <v>2592.6492800000001</v>
-      </c>
-      <c r="E16" s="43">
+        <v>1333.9882881249998</v>
+      </c>
+      <c r="E16" s="38">
         <f>E7*Assumptions!$E$13</f>
-        <v>2696.3552512000006</v>
-      </c>
-      <c r="F16" s="43">
+        <v>1407.3576439718747</v>
+      </c>
+      <c r="F16" s="38">
         <f>F7*Assumptions!$E$13</f>
-        <v>2804.2094612480005</v>
-      </c>
-      <c r="G16" s="43">
+        <v>1484.7623143903277</v>
+      </c>
+      <c r="G16" s="38">
         <f>G7*Assumptions!$E$13</f>
-        <v>2916.3778396979205</v>
+        <v>1566.4242416817956</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>43</v>
-      </c>
-      <c r="C17" s="43">
+        <v>42</v>
+      </c>
+      <c r="C17" s="38">
         <f>C7*Assumptions!$E$14</f>
-        <v>2991.5183999999999</v>
-      </c>
-      <c r="D17" s="43">
+        <v>2023.1101999999998</v>
+      </c>
+      <c r="D17" s="38">
         <f>D7*Assumptions!$E$14</f>
-        <v>3111.1791359999997</v>
-      </c>
-      <c r="E17" s="43">
+        <v>2134.3812609999995</v>
+      </c>
+      <c r="E17" s="38">
         <f>E7*Assumptions!$E$14</f>
-        <v>3235.6263014400001</v>
-      </c>
-      <c r="F17" s="43">
+        <v>2251.7722303549995</v>
+      </c>
+      <c r="F17" s="38">
         <f>F7*Assumptions!$E$14</f>
-        <v>3365.0513534976003</v>
-      </c>
-      <c r="G17" s="43">
+        <v>2375.6197030245244</v>
+      </c>
+      <c r="G17" s="38">
         <f>G7*Assumptions!$E$14</f>
-        <v>3499.6534076375042</v>
+        <v>2506.2787866908729</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>44</v>
-      </c>
-      <c r="C18" s="43">
+        <v>43</v>
+      </c>
+      <c r="C18" s="38">
         <f>C7*Assumptions!$E$15</f>
-        <v>498.58640000000003</v>
-      </c>
-      <c r="D18" s="43">
+        <v>505.77754999999996</v>
+      </c>
+      <c r="D18" s="38">
         <f>D7*Assumptions!$E$15</f>
-        <v>518.529856</v>
-      </c>
-      <c r="E18" s="43">
+        <v>533.59531524999989</v>
+      </c>
+      <c r="E18" s="38">
         <f>E7*Assumptions!$E$15</f>
-        <v>539.27105024000002</v>
-      </c>
-      <c r="F18" s="43">
+        <v>562.94305758874987</v>
+      </c>
+      <c r="F18" s="38">
         <f>F7*Assumptions!$E$15</f>
-        <v>560.84189224960005</v>
-      </c>
-      <c r="G18" s="43">
+        <v>593.90492575613109</v>
+      </c>
+      <c r="G18" s="38">
         <f>G7*Assumptions!$E$15</f>
-        <v>583.27556793958411</v>
+        <v>626.56969667271824</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>8</v>
-      </c>
-      <c r="B21" s="54" t="s">
-        <v>55</v>
-      </c>
-      <c r="C21" s="13">
+        <v>7</v>
+      </c>
+      <c r="B21" s="48" t="s">
+        <v>51</v>
+      </c>
+      <c r="C21" s="9">
         <v>2026</v>
       </c>
-      <c r="D21" s="13">
+      <c r="D21" s="9">
         <f>C21+1</f>
         <v>2027</v>
       </c>
-      <c r="E21" s="13">
+      <c r="E21" s="9">
         <f>D21+1</f>
         <v>2028</v>
       </c>
-      <c r="F21" s="13">
+      <c r="F21" s="9">
         <f>E21+1</f>
         <v>2029</v>
       </c>
-      <c r="G21" s="13">
+      <c r="G21" s="9">
         <f>F21+1</f>
         <v>2030</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>47</v>
-      </c>
-      <c r="C22" s="43">
+        <v>83</v>
+      </c>
+      <c r="C22" s="38">
         <f>C12+C16-C17-C18</f>
-        <v>9752.3499840000004</v>
-      </c>
-      <c r="D22" s="43">
+        <v>10224.293173249998</v>
+      </c>
+      <c r="D22" s="38">
         <f>D12+D16-D17-D18</f>
-        <v>10142.443983360003</v>
-      </c>
-      <c r="E22" s="43">
+        <v>10786.629297778749</v>
+      </c>
+      <c r="E22" s="38">
         <f>E12+E16-E17-E18</f>
-        <v>10548.141742694403</v>
-      </c>
-      <c r="F22" s="43">
+        <v>11379.893909156579</v>
+      </c>
+      <c r="F22" s="38">
         <f>F12+F16-F17-F18</f>
-        <v>10970.067412402179</v>
-      </c>
-      <c r="G22" s="43">
+        <v>12005.788074160189</v>
+      </c>
+      <c r="G22" s="38">
         <f>G12+G16-G17-G18</f>
-        <v>11408.870108898267</v>
+        <v>12666.106418238996</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="F26" s="52"/>
+      <c r="F26" s="46"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2399,167 +2523,167 @@
     <col min="4" max="6" width="16.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:4" s="52" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="53" t="s">
-        <v>56</v>
+    <row r="2" spans="1:4" s="46" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="47" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D4" s="56"/>
+      <c r="D4" s="50"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="C5" s="13"/>
+        <v>7</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C5" s="9"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="57">
+        <v>21</v>
+      </c>
+      <c r="C6" s="51">
         <f>Assumptions!E18</f>
         <v>0.04</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="58">
+        <v>23</v>
+      </c>
+      <c r="C7" s="52">
         <f>Assumptions!E20</f>
         <v>0.6</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="59">
+        <v>22</v>
+      </c>
+      <c r="C8" s="53">
         <f>Assumptions!E19</f>
         <v>5.5E-2</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>58</v>
-      </c>
-      <c r="C9" s="57">
+        <v>54</v>
+      </c>
+      <c r="C9" s="51">
         <f>C6+C7*C8</f>
         <v>7.3000000000000009E-2</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" s="13"/>
+        <v>7</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="9"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>59</v>
-      </c>
-      <c r="C13" s="57">
+        <v>55</v>
+      </c>
+      <c r="C13" s="51">
         <f>Assumptions!E21</f>
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>17</v>
-      </c>
-      <c r="C14" s="60">
+        <v>16</v>
+      </c>
+      <c r="C14" s="54">
         <f>Assumptions!E12</f>
         <v>0.23</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>60</v>
-      </c>
-      <c r="C15" s="57">
+        <v>56</v>
+      </c>
+      <c r="C15" s="51">
         <f>C13*(1-C14)</f>
         <v>3.465E-2</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>8</v>
-      </c>
-      <c r="B18" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="C18" s="15"/>
+        <v>7</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C18" s="11"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>62</v>
-      </c>
-      <c r="C19" s="60">
+        <v>58</v>
+      </c>
+      <c r="C19" s="54">
         <f>Assumptions!E23</f>
         <v>0.7</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>63</v>
-      </c>
-      <c r="C20" s="60">
+        <v>59</v>
+      </c>
+      <c r="C20" s="54">
         <f>Assumptions!E22</f>
         <v>0.3</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>64</v>
-      </c>
-      <c r="C21" s="60">
+        <v>60</v>
+      </c>
+      <c r="C21" s="54">
         <f>C19+C20</f>
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>65</v>
-      </c>
-      <c r="C22" s="60">
+        <v>61</v>
+      </c>
+      <c r="C22" s="54">
         <f>C19/C21</f>
         <v>0.7</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>66</v>
-      </c>
-      <c r="C23" s="60">
+        <v>62</v>
+      </c>
+      <c r="C23" s="54">
         <f>C20/C21</f>
         <v>0.3</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B25" s="61"/>
-      <c r="C25" s="61"/>
+      <c r="B25" s="55"/>
+      <c r="C25" s="55"/>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="26" t="s">
-        <v>8</v>
-      </c>
-      <c r="B26" s="62" t="s">
-        <v>67</v>
-      </c>
-      <c r="C26" s="63">
+      <c r="A26" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="B26" s="56" t="s">
+        <v>63</v>
+      </c>
+      <c r="C26" s="70">
         <f>(C22*C9)+(C23*C15)</f>
         <v>6.1495000000000008E-2</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B28" s="51"/>
+      <c r="B28" s="45"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2578,262 +2702,255 @@
     <col min="4" max="8" width="16.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8" s="52" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="53" t="s">
-        <v>68</v>
+    <row r="2" spans="1:8" s="46" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="47" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B4" s="40" t="s">
-        <v>31</v>
+      <c r="B4" s="35" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="C5" s="13">
+        <v>7</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5" s="9">
         <v>2026</v>
       </c>
-      <c r="D5" s="13">
+      <c r="D5" s="9">
         <f>C5+1</f>
         <v>2027</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="9">
         <f>D5+1</f>
         <v>2028</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="9">
         <f>E5+1</f>
         <v>2029</v>
       </c>
-      <c r="G5" s="13">
+      <c r="G5" s="9">
         <f>F5+1</f>
         <v>2030</v>
       </c>
-      <c r="H5" s="56"/>
+      <c r="H5" s="50"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>47</v>
-      </c>
-      <c r="C6" s="43">
+        <v>83</v>
+      </c>
+      <c r="C6" s="38">
         <f>Forecast!C22</f>
-        <v>9752.3499840000004</v>
-      </c>
-      <c r="D6" s="43">
+        <v>10224.293173249998</v>
+      </c>
+      <c r="D6" s="38">
         <f>Forecast!D22</f>
-        <v>10142.443983360003</v>
-      </c>
-      <c r="E6" s="43">
+        <v>10786.629297778749</v>
+      </c>
+      <c r="E6" s="38">
         <f>Forecast!E22</f>
-        <v>10548.141742694403</v>
-      </c>
-      <c r="F6" s="43">
+        <v>11379.893909156579</v>
+      </c>
+      <c r="F6" s="38">
         <f>Forecast!F22</f>
-        <v>10970.067412402179</v>
-      </c>
-      <c r="G6" s="43">
+        <v>12005.788074160189</v>
+      </c>
+      <c r="G6" s="38">
         <f>Forecast!G22</f>
-        <v>11408.870108898267</v>
+        <v>12666.106418238996</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C7" s="49">
+        <v>66</v>
+      </c>
+      <c r="C7" s="43">
         <f>1/(1+WACC!$C$26)</f>
         <v>0.94206755566441658</v>
       </c>
-      <c r="D7" s="49">
+      <c r="D7" s="43">
         <f>C7/(1+WACC!$C$26)</f>
         <v>0.88749127943552863</v>
       </c>
-      <c r="E7" s="49">
+      <c r="E7" s="43">
         <f>D7/(1+WACC!$C$26)</f>
         <v>0.83607674029131418</v>
       </c>
-      <c r="F7" s="49">
+      <c r="F7" s="43">
         <f>E7/(1+WACC!$C$26)</f>
         <v>0.78764077107411168</v>
       </c>
-      <c r="G7" s="49">
+      <c r="G7" s="43">
         <f>F7/(1+WACC!$C$26)</f>
         <v>0.74201081594742468</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>71</v>
-      </c>
-      <c r="C8" s="58">
+        <v>67</v>
+      </c>
+      <c r="C8" s="52">
         <f>C6*C7</f>
-        <v>9187.3725114107929</v>
-      </c>
-      <c r="D8" s="58">
+        <v>9631.9748781200069</v>
+      </c>
+      <c r="D8" s="52">
         <f>D6*D7</f>
-        <v>9001.3305873953486</v>
-      </c>
-      <c r="E8" s="58">
+        <v>9573.039436282419</v>
+      </c>
+      <c r="E8" s="52">
         <f>E6*E7</f>
-        <v>8819.0559643626784</v>
-      </c>
-      <c r="F8" s="58">
+        <v>9514.4646044286128</v>
+      </c>
+      <c r="F8" s="52">
         <f>F6*F7</f>
-        <v>8640.4723554394368</v>
-      </c>
-      <c r="G8" s="58">
+        <v>9456.2481760839055</v>
+      </c>
+      <c r="G8" s="52">
         <f>G6*G7</f>
-        <v>8465.5050185417876</v>
+        <v>9398.3879582744303</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D10" s="56"/>
-      <c r="E10" s="56"/>
-      <c r="F10" s="56"/>
-      <c r="G10" s="56"/>
+      <c r="D10" s="50"/>
+      <c r="E10" s="50"/>
+      <c r="F10" s="50"/>
+      <c r="G10" s="50"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="C11" s="13"/>
+        <v>7</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C11" s="9"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>29</v>
-      </c>
-      <c r="C12" s="64">
-        <v>2.5000000000000001E-2</v>
+        <v>28</v>
+      </c>
+      <c r="C12" s="57">
+        <f>Assumptions!E26</f>
+        <v>2.75E-2</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>73</v>
-      </c>
-      <c r="C13" s="43">
+        <v>69</v>
+      </c>
+      <c r="C13" s="38">
         <f>G6*(1+'Free Cash Flow'!C12)/(WACC!C26-'Free Cash Flow'!C12)</f>
-        <v>320429.97291740566</v>
+        <v>382833.48565202428</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>74</v>
-      </c>
-      <c r="C14" s="43">
+        <v>70</v>
+      </c>
+      <c r="C14" s="38">
         <f>C13/(1+WACC!C26)^5</f>
-        <v>237762.5056584554</v>
+        <v>284066.58706065529</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="E16" s="65"/>
-      <c r="F16" s="65"/>
-      <c r="G16" s="65"/>
+      <c r="E16" s="58"/>
+      <c r="F16" s="58"/>
+      <c r="G16" s="58"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>8</v>
-      </c>
-      <c r="B17" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C17" s="9"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B18" s="59" t="s">
+        <v>72</v>
+      </c>
+      <c r="C18" s="60">
+        <f>SUM(C8:G8)+C14</f>
+        <v>331640.70211384469</v>
+      </c>
+      <c r="D18" s="58"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B19" s="59" t="s">
+        <v>73</v>
+      </c>
+      <c r="C19" s="60">
+        <v>30069</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B20" s="59" t="s">
+        <v>74</v>
+      </c>
+      <c r="C20" s="60">
+        <f>C18-C19</f>
+        <v>301571.70211384469</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B21" s="59" t="s">
         <v>75</v>
       </c>
-      <c r="C17" s="13"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B18" s="66" t="s">
+      <c r="C21" s="60">
+        <v>7040</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B22" s="61" t="s">
         <v>76</v>
       </c>
-      <c r="C18" s="67">
-        <f>SUM(C8:G8)+C14</f>
-        <v>281876.24209560547</v>
-      </c>
-      <c r="D18" s="65"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B19" s="66" t="s">
+      <c r="C22" s="62">
+        <f>C20/C21</f>
+        <v>42.83688950480748</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B30" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="C19" s="67">
-        <v>30069</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B20" s="66" t="s">
-        <v>78</v>
-      </c>
-      <c r="C20" s="67">
-        <f>C18-C19</f>
-        <v>251807.24209560547</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B21" s="66" t="s">
-        <v>79</v>
-      </c>
-      <c r="C21" s="67">
-        <v>7040</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B22" s="68" t="s">
-        <v>80</v>
-      </c>
-      <c r="C22" s="69">
-        <f>C20/C21</f>
-        <v>35.768074161307595</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B30" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="8"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B31" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B32" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="C32" s="8"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="8"/>
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="C33" s="8"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="8"/>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B34" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="C34" s="8"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="8"/>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2852,67 +2969,67 @@
     <col min="9" max="9" width="15.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" s="52" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="53" t="s">
-        <v>86</v>
+    <row r="2" spans="1:10" s="46" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="47" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="70"/>
-      <c r="B4" s="70"/>
-      <c r="C4" s="70"/>
-      <c r="D4" s="70"/>
-      <c r="E4" s="70"/>
-      <c r="F4" s="70"/>
-      <c r="G4" s="70"/>
-      <c r="H4" s="70"/>
+      <c r="A4" s="63"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="63"/>
+      <c r="D4" s="63"/>
+      <c r="E4" s="63"/>
+      <c r="F4" s="63"/>
+      <c r="G4" s="63"/>
+      <c r="H4" s="63"/>
     </row>
     <row r="5" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="70"/>
-      <c r="B5" s="71" t="s">
-        <v>87</v>
-      </c>
-      <c r="D5" s="70"/>
-      <c r="E5" s="70"/>
-      <c r="F5" s="70"/>
-      <c r="G5" s="70"/>
-      <c r="H5" s="70"/>
+      <c r="A5" s="63"/>
+      <c r="B5" s="64" t="s">
+        <v>78</v>
+      </c>
+      <c r="D5" s="63"/>
+      <c r="E5" s="63"/>
+      <c r="F5" s="63"/>
+      <c r="G5" s="63"/>
+      <c r="H5" s="63"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="70"/>
-      <c r="B6" s="70"/>
-      <c r="C6" s="70"/>
-      <c r="D6" s="70"/>
-      <c r="E6" s="70"/>
-      <c r="F6" s="70"/>
-      <c r="G6" s="70"/>
-      <c r="H6" s="70"/>
+      <c r="A6" s="63"/>
+      <c r="B6" s="63"/>
+      <c r="C6" s="63"/>
+      <c r="D6" s="63"/>
+      <c r="E6" s="63"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="63"/>
+      <c r="H6" s="63"/>
     </row>
     <row r="7" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="70"/>
-      <c r="B7" s="70"/>
-      <c r="C7" s="70"/>
-      <c r="D7" s="72" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" s="70"/>
-      <c r="F7" s="70"/>
-      <c r="G7" s="70"/>
+      <c r="A7" s="63"/>
+      <c r="B7" s="63"/>
+      <c r="C7" s="63"/>
+      <c r="D7" s="65" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" s="63"/>
+      <c r="F7" s="63"/>
+      <c r="G7" s="63"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="70"/>
-      <c r="B8" s="73">
+      <c r="A8" s="63"/>
+      <c r="B8" s="66">
         <f>'Free Cash Flow'!C22</f>
-        <v>35.768074161307595</v>
-      </c>
-      <c r="C8" s="74">
+        <v>42.83688950480748</v>
+      </c>
+      <c r="C8" s="75">
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="D8" s="75">
         <v>0.02</v>
       </c>
       <c r="E8" s="76">
-        <v>2.5000000000000001E-2</v>
+        <v>2.75E-2</v>
       </c>
       <c r="F8" s="75">
         <v>0.03</v>
@@ -2920,199 +3037,199 @@
       <c r="G8" s="77">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="I8" s="78" t="s">
-        <v>88</v>
-      </c>
-      <c r="J8" s="79"/>
+      <c r="I8" s="67" t="s">
+        <v>79</v>
+      </c>
+      <c r="J8" s="68"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="70"/>
-      <c r="B9" s="80">
-        <v>0.06</v>
-      </c>
-      <c r="C9" s="81">
-        <f>(Forecast!C22/(1+$B$9)^1+Forecast!D22/(1+$B$9)^2+Forecast!E22/(1+$B$9)^3+Forecast!F22/(1+$B$9)^4+Forecast!G22/(1+$B$9)^5+(Forecast!G22*(1+C$8)/($B$9-C$8))/(1+$B$9)^5-'Free Cash Flow'!$C$19)/'Free Cash Flow'!$C$21</f>
-        <v>29.335749105255754</v>
-      </c>
-      <c r="D9" s="81">
-        <f>(Forecast!C22/(1+$B$9)^1+Forecast!D22/(1+$B$9)^2+Forecast!E22/(1+$B$9)^3+Forecast!F22/(1+$B$9)^4+Forecast!G22/(1+$B$9)^5+(Forecast!G22*(1+D$8)/($B$9-D$8))/(1+$B$9)^5-'Free Cash Flow'!$C$19)/'Free Cash Flow'!$C$21</f>
-        <v>32.901442649275644</v>
-      </c>
-      <c r="E9" s="82">
-        <f>(Forecast!C22/(1+$B$9)^1+Forecast!D22/(1+$B$9)^2+Forecast!E22/(1+$B$9)^3+Forecast!F22/(1+$B$9)^4+Forecast!G22/(1+$B$9)^5+(Forecast!G22*(1+E$8)/($B$9-E$8))/(1+$B$9)^5-'Free Cash Flow'!$C$19)/'Free Cash Flow'!$C$21</f>
-        <v>37.485905777301198</v>
-      </c>
-      <c r="F9" s="81">
-        <f>(Forecast!C22/(1+$B$9)^1+Forecast!D22/(1+$B$9)^2+Forecast!E22/(1+$B$9)^3+Forecast!F22/(1+$B$9)^4+Forecast!G22/(1+$B$9)^5+(Forecast!G22*(1+F$8)/($B$9-F$8))/(1+$B$9)^5-'Free Cash Flow'!$C$19)/'Free Cash Flow'!$C$21</f>
-        <v>43.598523281335275</v>
-      </c>
-      <c r="G9" s="83">
-        <f>(Forecast!C22/(1+$B$9)^1+Forecast!D22/(1+$B$9)^2+Forecast!E22/(1+$B$9)^3+Forecast!F22/(1+$B$9)^4+Forecast!G22/(1+$B$9)^5+(Forecast!G22*(1+G$8)/($B$9-G$8))/(1+$B$9)^5-'Free Cash Flow'!$C$19)/'Free Cash Flow'!$C$21</f>
-        <v>52.15618778698299</v>
-      </c>
-      <c r="I9" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="J9" s="84">
+      <c r="A9" s="63"/>
+      <c r="B9" s="71">
+        <v>5.1499999999999997E-2</v>
+      </c>
+      <c r="C9" s="85">
+        <f>(NPV($B9,Forecast!$C$22:$G$22)+Forecast!$G$22*(1+C$8)/($B9-C$8)/(1+$B9)^5-'Free Cash Flow'!$C$19)/'Free Cash Flow'!$C$21</f>
+        <v>41.603069203771611</v>
+      </c>
+      <c r="D9" s="86">
+        <f>(NPV($B9,Forecast!$C$22:$G$22)+Forecast!$G$22*(1+D$8)/($B9-D$8)/(1+$B9)^5-'Free Cash Flow'!$C$19)/'Free Cash Flow'!$C$21</f>
+        <v>48.003363609001887</v>
+      </c>
+      <c r="E9" s="87">
+        <f>(NPV($B9,Forecast!$C$22:$G$22)+Forecast!$G$22*(1+E$8)/($B9-E$8)/(1+$B9)^5-'Free Cash Flow'!$C$19)/'Free Cash Flow'!$C$21</f>
+        <v>62.604035220933469</v>
+      </c>
+      <c r="F9" s="86">
+        <f>(NPV($B9,Forecast!$C$22:$G$22)+Forecast!$G$22*(1+F$8)/($B9-F$8)/(1+$B9)^5-'Free Cash Flow'!$C$19)/'Free Cash Flow'!$C$21</f>
+        <v>69.734595775597711</v>
+      </c>
+      <c r="G9" s="88">
+        <f>(NPV($B9,Forecast!$C$22:$G$22)+Forecast!$G$22*(1+G$8)/($B9-G$8)/(1+$B9)^5-'Free Cash Flow'!$C$19)/'Free Cash Flow'!$C$21</f>
+        <v>90.478044661893733</v>
+      </c>
+      <c r="I9" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="J9" s="78">
         <f>WACC!C26</f>
         <v>6.1495000000000008E-2</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="70"/>
-      <c r="B10" s="85">
-        <v>6.5000000000000002E-2</v>
-      </c>
-      <c r="C10" s="81">
-        <f>(Forecast!C22/(1+$B$10)^1+Forecast!D22/(1+$B$10)^2+Forecast!E22/(1+$B$10)^3+Forecast!F22/(1+$B$10)^4+Forecast!G22/(1+$B$10)^5+(Forecast!G22*(1+C$8)/($B$10-C$8))/(1+$B$10)^5-'Free Cash Flow'!$C$19)/'Free Cash Flow'!$C$21</f>
-        <v>25.945658498107171</v>
-      </c>
-      <c r="D10" s="81">
-        <f>(Forecast!C22/(1+$B$10)^1+Forecast!D22/(1+$B$10)^2+Forecast!E22/(1+$B$10)^3+Forecast!F22/(1+$B$10)^4+Forecast!G22/(1+$B$10)^5+(Forecast!G22*(1+D$8)/($B$10-D$8))/(1+$B$10)^5-'Free Cash Flow'!$C$19)/'Free Cash Flow'!$C$21</f>
-        <v>28.745020296297294</v>
-      </c>
-      <c r="E10" s="82">
-        <f>(Forecast!C22/(1+$B$10)^1+Forecast!D22/(1+$B$10)^2+Forecast!E22/(1+$B$10)^3+Forecast!F22/(1+$B$10)^4+Forecast!G22/(1+$B$10)^5+(Forecast!G22*(1+E$8)/($B$10-E$8))/(1+$B$10)^5-'Free Cash Flow'!$C$19)/'Free Cash Flow'!$C$21</f>
-        <v>32.244222544034926</v>
-      </c>
-      <c r="F10" s="81">
-        <f>(Forecast!C22/(1+$B$10)^1+Forecast!D22/(1+$B$10)^2+Forecast!E22/(1+$B$10)^3+Forecast!F22/(1+$B$10)^4+Forecast!G22/(1+$B$10)^5+(Forecast!G22*(1+F$8)/($B$10-F$8))/(1+$B$10)^5-'Free Cash Flow'!$C$19)/'Free Cash Flow'!$C$21</f>
-        <v>36.743196862554761</v>
-      </c>
-      <c r="G10" s="83">
-        <f>(Forecast!C22/(1+$B$10)^1+Forecast!D22/(1+$B$10)^2+Forecast!E22/(1+$B$10)^3+Forecast!F22/(1+$B$10)^4+Forecast!G22/(1+$B$10)^5+(Forecast!G22*(1+G$8)/($B$10-G$8))/(1+$B$10)^5-'Free Cash Flow'!$C$19)/'Free Cash Flow'!$C$21</f>
-        <v>42.741829287247874</v>
-      </c>
-      <c r="I10" s="28" t="s">
-        <v>90</v>
-      </c>
-      <c r="J10" s="86">
+      <c r="A10" s="63"/>
+      <c r="B10" s="72">
+        <v>5.6500000000000002E-2</v>
+      </c>
+      <c r="C10" s="89">
+        <f>(NPV($B10,Forecast!$C$22:$G$22)+Forecast!$G$22*(1+C$8)/($B10-C$8)/(1+$B10)^5-'Free Cash Flow'!$C$19)/'Free Cash Flow'!$C$21</f>
+        <v>36.012929171234106</v>
+      </c>
+      <c r="D10" s="90">
+        <f>(NPV($B10,Forecast!$C$22:$G$22)+Forecast!$G$22*(1+D$8)/($B10-D$8)/(1+$B10)^5-'Free Cash Flow'!$C$19)/'Free Cash Flow'!$C$21</f>
+        <v>40.779669685906505</v>
+      </c>
+      <c r="E10" s="91">
+        <f>(NPV($B10,Forecast!$C$22:$G$22)+Forecast!$G$22*(1+E$8)/($B10-E$8)/(1+$B10)^5-'Free Cash Flow'!$C$19)/'Free Cash Flow'!$C$21</f>
+        <v>51.011724756194688</v>
+      </c>
+      <c r="F10" s="90">
+        <f>(NPV($B10,Forecast!$C$22:$G$22)+Forecast!$G$22*(1+F$8)/($B10-F$8)/(1+$B10)^5-'Free Cash Flow'!$C$19)/'Free Cash Flow'!$C$21</f>
+        <v>55.709460731861576</v>
+      </c>
+      <c r="G10" s="92">
+        <f>(NPV($B10,Forecast!$C$22:$G$22)+Forecast!$G$22*(1+G$8)/($B10-G$8)/(1+$B10)^5-'Free Cash Flow'!$C$19)/'Free Cash Flow'!$C$21</f>
+        <v>68.382422898776937</v>
+      </c>
+      <c r="I10" s="24" t="s">
+        <v>81</v>
+      </c>
+      <c r="J10" s="83">
         <f>'Free Cash Flow'!C12</f>
-        <v>2.5000000000000001E-2</v>
+        <v>2.75E-2</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="87"/>
-      <c r="B11" s="88">
-        <v>6.6699999999999995E-2</v>
-      </c>
-      <c r="C11" s="82">
-        <f>(Forecast!C22/(1+$B$11)^1+Forecast!D22/(1+$B$11)^2+Forecast!E22/(1+$B$11)^3+Forecast!F22/(1+$B$11)^4+Forecast!G22/(1+$B$11)^5+(Forecast!G22*(1+C$8)/($B$11-C$8))/(1+$B$11)^5-'Free Cash Flow'!$C$19)/'Free Cash Flow'!$C$21</f>
-        <v>24.94252194066522</v>
-      </c>
-      <c r="D11" s="82">
-        <f>(Forecast!C22/(1+$B$11)^1+Forecast!D22/(1+$B$11)^2+Forecast!E22/(1+$B$11)^3+Forecast!F22/(1+$B$11)^4+Forecast!G22/(1+$B$11)^5+(Forecast!G22*(1+D$8)/($B$11-D$8))/(1+$B$11)^5-'Free Cash Flow'!$C$19)/'Free Cash Flow'!$C$21</f>
-        <v>27.534691324459899</v>
-      </c>
-      <c r="E11" s="82">
-        <f>(Forecast!C22/(1+$B$11)^1+Forecast!D22/(1+$B$11)^2+Forecast!E22/(1+$B$11)^3+Forecast!F22/(1+$B$11)^4+Forecast!G22/(1+$B$11)^5+(Forecast!G22*(1+E$8)/($B$11-E$8))/(1+$B$11)^5-'Free Cash Flow'!$C$19)/'Free Cash Flow'!$C$21</f>
-        <v>30.748484061682557</v>
-      </c>
-      <c r="F11" s="82">
-        <f>(Forecast!C22/(1+$B$11)^1+Forecast!D22/(1+$B$11)^2+Forecast!E22/(1+$B$11)^3+Forecast!F22/(1+$B$11)^4+Forecast!G22/(1+$B$11)^5+(Forecast!G22*(1+F$8)/($B$11-F$8))/(1+$B$11)^5-'Free Cash Flow'!$C$19)/'Free Cash Flow'!$C$21</f>
-        <v>34.837969642835098</v>
-      </c>
-      <c r="G11" s="89">
-        <f>(Forecast!C22/(1+$B$11)^1+Forecast!D22/(1+$B$11)^2+Forecast!E22/(1+$B$11)^3+Forecast!F22/(1+$B$11)^4+Forecast!G22/(1+$B$11)^5+(Forecast!G22*(1+G$8)/($B$11-G$8))/(1+$B$11)^5-'Free Cash Flow'!$C$19)/'Free Cash Flow'!$C$21</f>
-        <v>40.217513766937969</v>
+      <c r="A11" s="69"/>
+      <c r="B11" s="73">
+        <v>6.1499999999999999E-2</v>
+      </c>
+      <c r="C11" s="93">
+        <f>(NPV($B11,Forecast!$C$22:$G$22)+Forecast!$G$22*(1+C$8)/($B11-C$8)/(1+$B11)^5-'Free Cash Flow'!$C$19)/'Free Cash Flow'!$C$21</f>
+        <v>31.626025874695522</v>
+      </c>
+      <c r="D11" s="91">
+        <f>(NPV($B11,Forecast!$C$22:$G$22)+Forecast!$G$22*(1+D$8)/($B11-D$8)/(1+$B11)^5-'Free Cash Flow'!$C$19)/'Free Cash Flow'!$C$21</f>
+        <v>35.297660308406478</v>
+      </c>
+      <c r="E11" s="94">
+        <f>(NPV($B11,Forecast!$C$22:$G$22)+Forecast!$G$22*(1+E$8)/($B11-E$8)/(1+$B11)^5-'Free Cash Flow'!$C$19)/'Free Cash Flow'!$C$21</f>
+        <v>42.829910359916433</v>
+      </c>
+      <c r="F11" s="91">
+        <f>(NPV($B11,Forecast!$C$22:$G$22)+Forecast!$G$22*(1+F$8)/($B11-F$8)/(1+$B11)^5-'Free Cash Flow'!$C$19)/'Free Cash Flow'!$C$21</f>
+        <v>46.137723874600702</v>
+      </c>
+      <c r="G11" s="95">
+        <f>(NPV($B11,Forecast!$C$22:$G$22)+Forecast!$G$22*(1+G$8)/($B11-G$8)/(1+$B11)^5-'Free Cash Flow'!$C$19)/'Free Cash Flow'!$C$21</f>
+        <v>54.625698176432032</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="70"/>
-      <c r="B12" s="85">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="C12" s="81">
-        <f>(Forecast!C22/(1+$B$12)^1+Forecast!D22/(1+$B$12)^2+Forecast!E22/(1+$B$12)^3+Forecast!F22/(1+$B$12)^4+Forecast!G22/(1+$B$12)^5+(Forecast!G22*(1+C$8)/($B$12-C$8))/(1+$B$12)^5-'Free Cash Flow'!$C$19)/'Free Cash Flow'!$C$21</f>
-        <v>20.861870907581068</v>
-      </c>
-      <c r="D12" s="81">
-        <f>(Forecast!C22/(1+$B$12)^1+Forecast!D22/(1+$B$12)^2+Forecast!E22/(1+$B$12)^3+Forecast!F22/(1+$B$12)^4+Forecast!G22/(1+$B$12)^5+(Forecast!G22*(1+D$8)/($B$12-D$8))/(1+$B$12)^5-'Free Cash Flow'!$C$19)/'Free Cash Flow'!$C$21</f>
-        <v>22.700491771409595</v>
-      </c>
-      <c r="E12" s="82">
-        <f>(Forecast!C22/(1+$B$12)^1+Forecast!D22/(1+$B$12)^2+Forecast!E22/(1+$B$12)^3+Forecast!F22/(1+$B$12)^4+Forecast!G22/(1+$B$12)^5+(Forecast!G22*(1+E$8)/($B$12-E$8))/(1+$B$12)^5-'Free Cash Flow'!$C$19)/'Free Cash Flow'!$C$21</f>
-        <v>24.906836808003824</v>
-      </c>
-      <c r="F12" s="81">
-        <f>(Forecast!C22/(1+$B$12)^1+Forecast!D22/(1+$B$12)^2+Forecast!E22/(1+$B$12)^3+Forecast!F22/(1+$B$12)^4+Forecast!G22/(1+$B$12)^5+(Forecast!G22*(1+F$8)/($B$12-F$8))/(1+$B$12)^5-'Free Cash Flow'!$C$19)/'Free Cash Flow'!$C$21</f>
-        <v>27.603480741618998</v>
-      </c>
-      <c r="G12" s="83">
-        <f>(Forecast!C22/(1+$B$12)^1+Forecast!D22/(1+$B$12)^2+Forecast!E22/(1+$B$12)^3+Forecast!F22/(1+$B$12)^4+Forecast!G22/(1+$B$12)^5+(Forecast!G22*(1+G$8)/($B$12-G$8))/(1+$B$12)^5-'Free Cash Flow'!$C$19)/'Free Cash Flow'!$C$21</f>
-        <v>30.974285658637967</v>
-      </c>
-      <c r="H12" s="70"/>
+      <c r="A12" s="63"/>
+      <c r="B12" s="72">
+        <v>6.6500000000000004E-2</v>
+      </c>
+      <c r="C12" s="89">
+        <f>(NPV($B12,Forecast!$C$22:$G$22)+Forecast!$G$22*(1+C$8)/($B12-C$8)/(1+$B12)^5-'Free Cash Flow'!$C$19)/'Free Cash Flow'!$C$21</f>
+        <v>28.091878679197688</v>
+      </c>
+      <c r="D12" s="90">
+        <f>(NPV($B12,Forecast!$C$22:$G$22)+Forecast!$G$22*(1+D$8)/($B12-D$8)/(1+$B12)^5-'Free Cash Flow'!$C$19)/'Free Cash Flow'!$C$21</f>
+        <v>30.995479140227655</v>
+      </c>
+      <c r="E12" s="91">
+        <f>(NPV($B12,Forecast!$C$22:$G$22)+Forecast!$G$22*(1+E$8)/($B12-E$8)/(1+$B12)^5-'Free Cash Flow'!$C$19)/'Free Cash Flow'!$C$21</f>
+        <v>36.746841591883161</v>
+      </c>
+      <c r="F12" s="90">
+        <f>(NPV($B12,Forecast!$C$22:$G$22)+Forecast!$G$22*(1+F$8)/($B12-F$8)/(1+$B12)^5-'Free Cash Flow'!$C$19)/'Free Cash Flow'!$C$21</f>
+        <v>39.18920098916152</v>
+      </c>
+      <c r="G12" s="92">
+        <f>(NPV($B12,Forecast!$C$22:$G$22)+Forecast!$G$22*(1+G$8)/($B12-G$8)/(1+$B12)^5-'Free Cash Flow'!$C$19)/'Free Cash Flow'!$C$21</f>
+        <v>45.23694806813652</v>
+      </c>
+      <c r="H12" s="63"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="70"/>
-      <c r="B13" s="90">
-        <v>0.08</v>
-      </c>
-      <c r="C13" s="91">
-        <f>(Forecast!C22/(1+$B$13)^1+Forecast!D22/(1+$B$13)^2+Forecast!E22/(1+$B$13)^3+Forecast!F22/(1+$B$13)^4+Forecast!G22/(1+$B$13)^5+(Forecast!G22*(1+C$8)/($B$13-C$8))/(1+$B$13)^5-'Free Cash Flow'!$C$19)/'Free Cash Flow'!$C$21</f>
-        <v>18.907170347577924</v>
-      </c>
-      <c r="D13" s="92">
-        <f>(Forecast!C22/(1+$B$13)^1+Forecast!D22/(1+$B$13)^2+Forecast!E22/(1+$B$13)^3+Forecast!F22/(1+$B$13)^4+Forecast!G22/(1+$B$13)^5+(Forecast!G22*(1+D$8)/($B$13-D$8))/(1+$B$13)^5-'Free Cash Flow'!$C$19)/'Free Cash Flow'!$C$21</f>
-        <v>20.434315619416026</v>
-      </c>
-      <c r="E13" s="93">
-        <f>(Forecast!C22/(1+$B$13)^1+Forecast!D22/(1+$B$13)^2+Forecast!E22/(1+$B$13)^3+Forecast!F22/(1+$B$13)^4+Forecast!G22/(1+$B$13)^5+(Forecast!G22*(1+E$8)/($B$13-E$8))/(1+$B$13)^5-'Free Cash Flow'!$C$19)/'Free Cash Flow'!$C$21</f>
-        <v>22.239123667951951</v>
-      </c>
-      <c r="F13" s="92">
-        <f>(Forecast!C22/(1+$B$13)^1+Forecast!D22/(1+$B$13)^2+Forecast!E22/(1+$B$13)^3+Forecast!F22/(1+$B$13)^4+Forecast!G22/(1+$B$13)^5+(Forecast!G22*(1+F$8)/($B$13-F$8))/(1+$B$13)^5-'Free Cash Flow'!$C$19)/'Free Cash Flow'!$C$21</f>
-        <v>24.404893326195069</v>
-      </c>
-      <c r="G13" s="94">
-        <f>(Forecast!C22/(1+$B$13)^1+Forecast!D22/(1+$B$13)^2+Forecast!E22/(1+$B$13)^3+Forecast!F22/(1+$B$13)^4+Forecast!G22/(1+$B$13)^5+(Forecast!G22*(1+G$8)/($B$13-G$8))/(1+$B$13)^5-'Free Cash Flow'!$C$19)/'Free Cash Flow'!$C$21</f>
-        <v>27.051945130714433</v>
-      </c>
-      <c r="H13" s="70"/>
+      <c r="A13" s="63"/>
+      <c r="B13" s="74">
+        <v>7.1499999999999994E-2</v>
+      </c>
+      <c r="C13" s="96">
+        <f>(NPV($B13,Forecast!$C$22:$G$22)+Forecast!$G$22*(1+C$8)/($B13-C$8)/(1+$B13)^5-'Free Cash Flow'!$C$19)/'Free Cash Flow'!$C$21</f>
+        <v>25.184071522594191</v>
+      </c>
+      <c r="D13" s="97">
+        <f>(NPV($B13,Forecast!$C$22:$G$22)+Forecast!$G$22*(1+D$8)/($B13-D$8)/(1+$B13)^5-'Free Cash Flow'!$C$19)/'Free Cash Flow'!$C$21</f>
+        <v>27.529467086495846</v>
+      </c>
+      <c r="E13" s="98">
+        <f>(NPV($B13,Forecast!$C$22:$G$22)+Forecast!$G$22*(1+E$8)/($B13-E$8)/(1+$B13)^5-'Free Cash Flow'!$C$19)/'Free Cash Flow'!$C$21</f>
+        <v>32.047018769238228</v>
+      </c>
+      <c r="F13" s="97">
+        <f>(NPV($B13,Forecast!$C$22:$G$22)+Forecast!$G$22*(1+F$8)/($B13-F$8)/(1+$B13)^5-'Free Cash Flow'!$C$19)/'Free Cash Flow'!$C$21</f>
+        <v>33.915724886999129</v>
+      </c>
+      <c r="G13" s="99">
+        <f>(NPV($B13,Forecast!$C$22:$G$22)+Forecast!$G$22*(1+G$8)/($B13-G$8)/(1+$B13)^5-'Free Cash Flow'!$C$19)/'Free Cash Flow'!$C$21</f>
+        <v>38.42109854077885</v>
+      </c>
+      <c r="H13" s="63"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="70"/>
-      <c r="B14" s="70"/>
-      <c r="C14" s="70"/>
-      <c r="D14" s="70"/>
-      <c r="E14" s="70"/>
-      <c r="F14" s="70"/>
-      <c r="G14" s="70"/>
-      <c r="H14" s="70"/>
+      <c r="A14" s="63"/>
+      <c r="B14" s="63"/>
+      <c r="C14" s="63"/>
+      <c r="D14" s="63"/>
+      <c r="E14" s="63"/>
+      <c r="F14" s="63"/>
+      <c r="G14" s="63"/>
+      <c r="H14" s="63"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="70"/>
-      <c r="B15" s="70"/>
-      <c r="C15" s="70"/>
-      <c r="D15" s="70"/>
-      <c r="E15" s="70"/>
-      <c r="F15" s="70"/>
-      <c r="G15" s="70"/>
-      <c r="H15" s="70"/>
+      <c r="A15" s="63"/>
+      <c r="B15" s="63"/>
+      <c r="C15" s="63"/>
+      <c r="D15" s="63"/>
+      <c r="E15" s="63"/>
+      <c r="F15" s="63"/>
+      <c r="G15" s="63"/>
+      <c r="H15" s="63"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B17" s="70"/>
-      <c r="C17" s="70"/>
-      <c r="D17" s="70"/>
-      <c r="E17" s="70"/>
-      <c r="F17" s="70"/>
-      <c r="G17" s="70"/>
-      <c r="H17" s="70"/>
-      <c r="I17" s="70"/>
+      <c r="B17" s="63"/>
+      <c r="C17" s="63"/>
+      <c r="D17" s="63"/>
+      <c r="E17" s="63"/>
+      <c r="F17" s="63"/>
+      <c r="G17" s="63"/>
+      <c r="H17" s="63"/>
+      <c r="I17" s="63"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="70"/>
-      <c r="B18" s="70"/>
-      <c r="C18" s="70"/>
-      <c r="D18" s="70"/>
-      <c r="E18" s="70"/>
+      <c r="A18" s="63"/>
+      <c r="B18" s="63"/>
+      <c r="C18" s="63"/>
+      <c r="D18" s="63"/>
+      <c r="E18" s="63"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="70"/>
-      <c r="B24" s="70"/>
-      <c r="C24" s="70"/>
-      <c r="D24" s="70"/>
+      <c r="A24" s="63"/>
+      <c r="B24" s="63"/>
+      <c r="C24" s="63"/>
+      <c r="D24" s="63"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
